--- a/education_forms/044_student_internet_access_at_home_feedback_form--education_forms.xlsx
+++ b/education_forms/044_student_internet_access_at_home_feedback_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1202,8 +1202,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1741,12 +1741,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1775,12 +1775,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1809,12 +1809,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1826,12 +1826,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1843,12 +1843,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1877,12 +1877,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1894,12 +1894,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1911,12 +1911,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1928,12 +1928,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2030,12 +2030,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2064,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2115,12 +2115,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2166,12 +2166,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2183,12 +2183,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
